--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.74824</v>
+        <v>16.91513</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50219</v>
+        <v>16.74893</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53553</v>
+        <v>16.76306</v>
       </c>
       <c r="F2" t="n">
-        <v>42.76045</v>
+        <v>41.97391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05054</v>
+        <v>0.05091</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82515</v>
+        <v>1.84914</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.80022</v>
+        <v>17.17867</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4143</v>
+        <v>16.37722</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64531</v>
+        <v>16.78912</v>
       </c>
       <c r="F3" t="n">
-        <v>43.2389</v>
+        <v>42.63755</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05168</v>
+        <v>0.05038</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79936</v>
+        <v>1.84563</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.76755</v>
+        <v>17.01787</v>
       </c>
       <c r="D4" t="n">
-        <v>16.74116</v>
+        <v>16.62406</v>
       </c>
       <c r="E4" t="n">
-        <v>16.52083</v>
+        <v>16.91802</v>
       </c>
       <c r="F4" t="n">
-        <v>42.60618</v>
+        <v>43.11489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05066</v>
+        <v>0.05122</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83319</v>
+        <v>1.81531</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87082</v>
+        <v>16.68248</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18634</v>
+        <v>16.22144</v>
       </c>
       <c r="E6" t="n">
-        <v>16.29325</v>
+        <v>16.61171</v>
       </c>
       <c r="F6" t="n">
-        <v>22.23578</v>
+        <v>21.81473</v>
       </c>
       <c r="G6" t="n">
-        <v>33.79359</v>
+        <v>34.84231</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.73886</v>
+        <v>16.64549</v>
       </c>
       <c r="D7" t="n">
-        <v>16.18523</v>
+        <v>15.86893</v>
       </c>
       <c r="E7" t="n">
-        <v>16.57577</v>
+        <v>16.51047</v>
       </c>
       <c r="F7" t="n">
-        <v>22.04849</v>
+        <v>22.07649</v>
       </c>
       <c r="G7" t="n">
-        <v>34.74859</v>
+        <v>33.88363</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.11867</v>
+        <v>17.06704</v>
       </c>
       <c r="D8" t="n">
-        <v>16.37435</v>
+        <v>16.09419</v>
       </c>
       <c r="E8" t="n">
-        <v>16.4092</v>
+        <v>16.38013</v>
       </c>
       <c r="F8" t="n">
-        <v>21.53225</v>
+        <v>22.13576</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0884</v>
+        <v>35.11236</v>
       </c>
     </row>
   </sheetData>
